--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -1856,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117868864</v>
+        <v>117868870</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57398</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,20 +1868,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1889,17 +1889,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478503</v>
+        <v>478261</v>
       </c>
       <c r="R12" t="n">
-        <v>6950950</v>
+        <v>6950705</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,11 +1948,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,7 +1974,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117868868</v>
+        <v>117868865</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -2003,10 +2014,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478526</v>
+        <v>478277</v>
       </c>
       <c r="R13" t="n">
-        <v>6951080</v>
+        <v>6950566</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2070,7 +2081,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117868865</v>
+        <v>117868866</v>
       </c>
       <c r="B14" t="n">
         <v>57287</v>
@@ -2110,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478277</v>
+        <v>478227</v>
       </c>
       <c r="R14" t="n">
-        <v>6950566</v>
+        <v>6950630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117868869</v>
+        <v>117868864</v>
       </c>
       <c r="B15" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,21 +2204,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2217,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478247</v>
+        <v>478503</v>
       </c>
       <c r="R15" t="n">
-        <v>6950677</v>
+        <v>6950950</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,6 +2264,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117868870</v>
+        <v>117868867</v>
       </c>
       <c r="B16" t="n">
-        <v>57398</v>
+        <v>57287</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,20 +2307,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2312,33 +2328,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478261</v>
+        <v>478375</v>
       </c>
       <c r="R16" t="n">
-        <v>6950705</v>
+        <v>6950870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,6 +2371,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117868866</v>
+        <v>117868869</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,21 +2418,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2437,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478227</v>
+        <v>478247</v>
       </c>
       <c r="R17" t="n">
-        <v>6950630</v>
+        <v>6950677</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,11 +2478,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,7 +2504,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117868867</v>
+        <v>117868868</v>
       </c>
       <c r="B18" t="n">
         <v>57287</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478375</v>
+        <v>478526</v>
       </c>
       <c r="R18" t="n">
-        <v>6950870</v>
+        <v>6951080</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -1859,7 +1859,7 @@
         <v>117868870</v>
       </c>
       <c r="B12" t="n">
-        <v>57398</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>117868865</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117868866</v>
+        <v>117868867</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478227</v>
+        <v>478375</v>
       </c>
       <c r="R14" t="n">
-        <v>6950630</v>
+        <v>6950870</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117868864</v>
+        <v>117868868</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478503</v>
+        <v>478526</v>
       </c>
       <c r="R15" t="n">
-        <v>6950950</v>
+        <v>6951080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117868867</v>
+        <v>117868864</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478375</v>
+        <v>478503</v>
       </c>
       <c r="R16" t="n">
-        <v>6950870</v>
+        <v>6950950</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117868869</v>
+        <v>117868866</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478247</v>
+        <v>478227</v>
       </c>
       <c r="R17" t="n">
-        <v>6950677</v>
+        <v>6950630</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,6 +2478,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117868868</v>
+        <v>117868869</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,21 +2525,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2544,10 +2549,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478526</v>
+        <v>478247</v>
       </c>
       <c r="R18" t="n">
-        <v>6951080</v>
+        <v>6950677</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2580,11 +2585,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2725,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178252</v>
+        <v>122178363</v>
       </c>
       <c r="B20" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478406</v>
+        <v>478331</v>
       </c>
       <c r="R20" t="n">
-        <v>6950869</v>
+        <v>6950917</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178452</v>
+        <v>122178456</v>
       </c>
       <c r="B22" t="n">
-        <v>78645</v>
+        <v>79762</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478438</v>
+        <v>478417</v>
       </c>
       <c r="R22" t="n">
-        <v>6951070</v>
+        <v>6951176</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178449</v>
+        <v>122178459</v>
       </c>
       <c r="B23" t="n">
-        <v>79726</v>
+        <v>97129</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478483</v>
+        <v>478424</v>
       </c>
       <c r="R23" t="n">
-        <v>6951051</v>
+        <v>6951178</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178463</v>
+        <v>122178448</v>
       </c>
       <c r="B25" t="n">
-        <v>98196</v>
+        <v>78645</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3247,25 +3247,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478493</v>
+        <v>478499</v>
       </c>
       <c r="R25" t="n">
-        <v>6951137</v>
+        <v>6951053</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178362</v>
+        <v>122178457</v>
       </c>
       <c r="B26" t="n">
-        <v>98092</v>
+        <v>79726</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3349,38 +3349,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478333</v>
+        <v>478413</v>
       </c>
       <c r="R26" t="n">
-        <v>6950917</v>
+        <v>6951171</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178363</v>
+        <v>122178453</v>
       </c>
       <c r="B27" t="n">
-        <v>78645</v>
+        <v>79726</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,34 +3455,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478331</v>
+        <v>478446</v>
       </c>
       <c r="R27" t="n">
-        <v>6950917</v>
+        <v>6951134</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,10 +3541,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178460</v>
+        <v>122178253</v>
       </c>
       <c r="B28" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3553,38 +3553,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478446</v>
+        <v>478328</v>
       </c>
       <c r="R28" t="n">
-        <v>6951151</v>
+        <v>6950727</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178457</v>
+        <v>122178447</v>
       </c>
       <c r="B29" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3659,34 +3659,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478413</v>
+        <v>478465</v>
       </c>
       <c r="R29" t="n">
-        <v>6951171</v>
+        <v>6950995</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178253</v>
+        <v>122178450</v>
       </c>
       <c r="B30" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3757,38 +3757,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478328</v>
+        <v>478475</v>
       </c>
       <c r="R30" t="n">
-        <v>6950727</v>
+        <v>6951076</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178450</v>
+        <v>122178446</v>
       </c>
       <c r="B31" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3859,38 +3859,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478475</v>
+        <v>478494</v>
       </c>
       <c r="R31" t="n">
-        <v>6951076</v>
+        <v>6950958</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178459</v>
+        <v>122178464</v>
       </c>
       <c r="B32" t="n">
         <v>97129</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478424</v>
+        <v>478526</v>
       </c>
       <c r="R32" t="n">
-        <v>6951178</v>
+        <v>6951125</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178442</v>
+        <v>122178252</v>
       </c>
       <c r="B33" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4063,38 +4063,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478328</v>
+        <v>478406</v>
       </c>
       <c r="R33" t="n">
-        <v>6951010</v>
+        <v>6950869</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178464</v>
+        <v>122178452</v>
       </c>
       <c r="B34" t="n">
-        <v>97129</v>
+        <v>78645</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478526</v>
+        <v>478438</v>
       </c>
       <c r="R34" t="n">
-        <v>6951125</v>
+        <v>6951070</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178446</v>
+        <v>122178361</v>
       </c>
       <c r="B35" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478494</v>
+        <v>478441</v>
       </c>
       <c r="R35" t="n">
-        <v>6950958</v>
+        <v>6950927</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4325,12 +4325,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178465</v>
+        <v>122178442</v>
       </c>
       <c r="B36" t="n">
-        <v>98196</v>
+        <v>78645</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4369,25 +4369,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4397,10 +4397,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478530</v>
+        <v>478328</v>
       </c>
       <c r="R36" t="n">
-        <v>6951133</v>
+        <v>6951010</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4427,12 +4427,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4459,10 +4459,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178444</v>
+        <v>122178463</v>
       </c>
       <c r="B37" t="n">
-        <v>97129</v>
+        <v>98196</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4475,34 +4475,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478443</v>
+        <v>478493</v>
       </c>
       <c r="R37" t="n">
-        <v>6950943</v>
+        <v>6951137</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4529,12 +4529,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4561,10 +4561,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178455</v>
+        <v>122178465</v>
       </c>
       <c r="B38" t="n">
-        <v>97129</v>
+        <v>98196</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478417</v>
+        <v>478530</v>
       </c>
       <c r="R38" t="n">
-        <v>6951155</v>
+        <v>6951133</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178453</v>
+        <v>122178451</v>
       </c>
       <c r="B39" t="n">
-        <v>79726</v>
+        <v>74739</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478446</v>
+        <v>478444</v>
       </c>
       <c r="R39" t="n">
-        <v>6951134</v>
+        <v>6951071</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178451</v>
+        <v>122178449</v>
       </c>
       <c r="B40" t="n">
-        <v>74739</v>
+        <v>79726</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,21 +4781,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478444</v>
+        <v>478483</v>
       </c>
       <c r="R40" t="n">
-        <v>6951071</v>
+        <v>6951051</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178443</v>
+        <v>122178362</v>
       </c>
       <c r="B41" t="n">
-        <v>78645</v>
+        <v>98092</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,38 +4879,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478359</v>
+        <v>478333</v>
       </c>
       <c r="R41" t="n">
-        <v>6950978</v>
+        <v>6950917</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178456</v>
+        <v>122178443</v>
       </c>
       <c r="B42" t="n">
-        <v>79762</v>
+        <v>78645</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478417</v>
+        <v>478359</v>
       </c>
       <c r="R42" t="n">
-        <v>6951176</v>
+        <v>6950978</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5071,7 +5071,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178361</v>
+        <v>122178444</v>
       </c>
       <c r="B43" t="n">
         <v>97129</v>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478441</v>
+        <v>478443</v>
       </c>
       <c r="R43" t="n">
-        <v>6950927</v>
+        <v>6950943</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178447</v>
+        <v>122178455</v>
       </c>
       <c r="B44" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5185,38 +5185,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478465</v>
+        <v>478417</v>
       </c>
       <c r="R44" t="n">
-        <v>6950995</v>
+        <v>6951155</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178448</v>
+        <v>122178460</v>
       </c>
       <c r="B45" t="n">
-        <v>78645</v>
+        <v>97129</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478499</v>
+        <v>478446</v>
       </c>
       <c r="R45" t="n">
-        <v>6951053</v>
+        <v>6951151</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178456</v>
+        <v>122178459</v>
       </c>
       <c r="B22" t="n">
-        <v>79762</v>
+        <v>97129</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478417</v>
+        <v>478424</v>
       </c>
       <c r="R22" t="n">
-        <v>6951176</v>
+        <v>6951178</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178459</v>
+        <v>122178456</v>
       </c>
       <c r="B23" t="n">
-        <v>97129</v>
+        <v>79762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478424</v>
+        <v>478417</v>
       </c>
       <c r="R23" t="n">
-        <v>6951178</v>
+        <v>6951176</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178451</v>
+        <v>122178449</v>
       </c>
       <c r="B39" t="n">
-        <v>74739</v>
+        <v>79726</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478444</v>
+        <v>478483</v>
       </c>
       <c r="R39" t="n">
-        <v>6951071</v>
+        <v>6951051</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178449</v>
+        <v>122178362</v>
       </c>
       <c r="B40" t="n">
-        <v>79726</v>
+        <v>98092</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4777,38 +4777,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478483</v>
+        <v>478333</v>
       </c>
       <c r="R40" t="n">
-        <v>6951051</v>
+        <v>6950917</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178362</v>
+        <v>122178451</v>
       </c>
       <c r="B41" t="n">
-        <v>98092</v>
+        <v>74739</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,38 +4879,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478333</v>
+        <v>478444</v>
       </c>
       <c r="R41" t="n">
-        <v>6950917</v>
+        <v>6951071</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2725,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178363</v>
+        <v>122178460</v>
       </c>
       <c r="B20" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,38 +2737,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478331</v>
+        <v>478446</v>
       </c>
       <c r="R20" t="n">
-        <v>6950917</v>
+        <v>6951151</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,10 +2827,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178454</v>
+        <v>122178442</v>
       </c>
       <c r="B21" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478433</v>
+        <v>478328</v>
       </c>
       <c r="R21" t="n">
-        <v>6951141</v>
+        <v>6951010</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178459</v>
+        <v>122178444</v>
       </c>
       <c r="B22" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2965,14 +2965,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478424</v>
+        <v>478443</v>
       </c>
       <c r="R22" t="n">
-        <v>6951178</v>
+        <v>6950943</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178456</v>
+        <v>122178465</v>
       </c>
       <c r="B23" t="n">
-        <v>79762</v>
+        <v>98206</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478417</v>
+        <v>478530</v>
       </c>
       <c r="R23" t="n">
-        <v>6951176</v>
+        <v>6951133</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178461</v>
+        <v>122178443</v>
       </c>
       <c r="B24" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3173,10 +3173,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478474</v>
+        <v>478359</v>
       </c>
       <c r="R24" t="n">
-        <v>6951157</v>
+        <v>6950978</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178448</v>
+        <v>122178252</v>
       </c>
       <c r="B25" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3247,38 +3247,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478499</v>
+        <v>478406</v>
       </c>
       <c r="R25" t="n">
-        <v>6951053</v>
+        <v>6950869</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,10 +3337,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178457</v>
+        <v>122178362</v>
       </c>
       <c r="B26" t="n">
-        <v>79726</v>
+        <v>98102</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3349,38 +3349,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478413</v>
+        <v>478333</v>
       </c>
       <c r="R26" t="n">
-        <v>6951171</v>
+        <v>6950917</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178453</v>
+        <v>122178446</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,34 +3455,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478446</v>
+        <v>478494</v>
       </c>
       <c r="R27" t="n">
-        <v>6951134</v>
+        <v>6950958</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178253</v>
+        <v>122178457</v>
       </c>
       <c r="B28" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3557,34 +3557,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478328</v>
+        <v>478413</v>
       </c>
       <c r="R28" t="n">
-        <v>6950727</v>
+        <v>6951171</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178447</v>
+        <v>122178463</v>
       </c>
       <c r="B29" t="n">
-        <v>78645</v>
+        <v>98206</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3655,38 +3655,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478465</v>
+        <v>478493</v>
       </c>
       <c r="R29" t="n">
-        <v>6950995</v>
+        <v>6951137</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178450</v>
+        <v>122178447</v>
       </c>
       <c r="B30" t="n">
-        <v>97129</v>
+        <v>78646</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3757,38 +3757,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478475</v>
+        <v>478465</v>
       </c>
       <c r="R30" t="n">
-        <v>6951076</v>
+        <v>6950995</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178446</v>
+        <v>122178461</v>
       </c>
       <c r="B31" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3863,34 +3863,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478494</v>
+        <v>478474</v>
       </c>
       <c r="R31" t="n">
-        <v>6950958</v>
+        <v>6951157</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178464</v>
+        <v>122178451</v>
       </c>
       <c r="B32" t="n">
-        <v>97129</v>
+        <v>74739</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3961,25 +3961,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478526</v>
+        <v>478444</v>
       </c>
       <c r="R32" t="n">
-        <v>6951125</v>
+        <v>6951071</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178252</v>
+        <v>122178455</v>
       </c>
       <c r="B33" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4087,14 +4087,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478406</v>
+        <v>478417</v>
       </c>
       <c r="R33" t="n">
-        <v>6950869</v>
+        <v>6951155</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178452</v>
+        <v>122178450</v>
       </c>
       <c r="B34" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478438</v>
+        <v>478475</v>
       </c>
       <c r="R34" t="n">
-        <v>6951070</v>
+        <v>6951076</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178361</v>
+        <v>122178464</v>
       </c>
       <c r="B35" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4291,14 +4291,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478441</v>
+        <v>478526</v>
       </c>
       <c r="R35" t="n">
-        <v>6950927</v>
+        <v>6951125</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4325,12 +4325,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178442</v>
+        <v>122178363</v>
       </c>
       <c r="B36" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4393,14 +4393,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478328</v>
+        <v>478331</v>
       </c>
       <c r="R36" t="n">
-        <v>6951010</v>
+        <v>6950917</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178463</v>
+        <v>122178454</v>
       </c>
       <c r="B37" t="n">
-        <v>98196</v>
+        <v>78646</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4471,25 +4471,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478493</v>
+        <v>478433</v>
       </c>
       <c r="R37" t="n">
-        <v>6951137</v>
+        <v>6951141</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178465</v>
+        <v>122178452</v>
       </c>
       <c r="B38" t="n">
-        <v>98196</v>
+        <v>78646</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4573,25 +4573,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478530</v>
+        <v>478438</v>
       </c>
       <c r="R38" t="n">
-        <v>6951133</v>
+        <v>6951070</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178449</v>
+        <v>122178448</v>
       </c>
       <c r="B39" t="n">
-        <v>79726</v>
+        <v>78646</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4679,21 +4679,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4703,10 +4703,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478483</v>
+        <v>478499</v>
       </c>
       <c r="R39" t="n">
-        <v>6951051</v>
+        <v>6951053</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178362</v>
+        <v>122178456</v>
       </c>
       <c r="B40" t="n">
-        <v>98092</v>
+        <v>79763</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,34 +4781,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478333</v>
+        <v>478417</v>
       </c>
       <c r="R40" t="n">
-        <v>6950917</v>
+        <v>6951176</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178451</v>
+        <v>122178459</v>
       </c>
       <c r="B41" t="n">
-        <v>74739</v>
+        <v>97139</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478444</v>
+        <v>478424</v>
       </c>
       <c r="R41" t="n">
-        <v>6951071</v>
+        <v>6951178</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178443</v>
+        <v>122178361</v>
       </c>
       <c r="B42" t="n">
-        <v>78645</v>
+        <v>97139</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,38 +4981,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478359</v>
+        <v>478441</v>
       </c>
       <c r="R42" t="n">
-        <v>6950978</v>
+        <v>6950927</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178444</v>
+        <v>122178449</v>
       </c>
       <c r="B43" t="n">
-        <v>97129</v>
+        <v>79727</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5083,38 +5083,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478443</v>
+        <v>478483</v>
       </c>
       <c r="R43" t="n">
-        <v>6950943</v>
+        <v>6951051</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5173,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178455</v>
+        <v>122178253</v>
       </c>
       <c r="B44" t="n">
-        <v>97129</v>
+        <v>78646</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5185,38 +5185,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478417</v>
+        <v>478328</v>
       </c>
       <c r="R44" t="n">
-        <v>6951155</v>
+        <v>6950727</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178460</v>
+        <v>122178453</v>
       </c>
       <c r="B45" t="n">
-        <v>97129</v>
+        <v>79727</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
         <v>478446</v>
       </c>
       <c r="R45" t="n">
-        <v>6951151</v>
+        <v>6951134</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2725,7 +2725,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178460</v>
+        <v>122178464</v>
       </c>
       <c r="B20" t="n">
         <v>97139</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478446</v>
+        <v>478526</v>
       </c>
       <c r="R20" t="n">
-        <v>6951151</v>
+        <v>6951125</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178442</v>
+        <v>122178447</v>
       </c>
       <c r="B21" t="n">
         <v>78646</v>
@@ -2863,14 +2863,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478328</v>
+        <v>478465</v>
       </c>
       <c r="R21" t="n">
-        <v>6951010</v>
+        <v>6950995</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178444</v>
+        <v>122178443</v>
       </c>
       <c r="B22" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,38 +2941,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478443</v>
+        <v>478359</v>
       </c>
       <c r="R22" t="n">
-        <v>6950943</v>
+        <v>6950978</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178465</v>
+        <v>122178451</v>
       </c>
       <c r="B23" t="n">
-        <v>98206</v>
+        <v>74739</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478530</v>
+        <v>478444</v>
       </c>
       <c r="R23" t="n">
-        <v>6951133</v>
+        <v>6951071</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178443</v>
+        <v>122178252</v>
       </c>
       <c r="B24" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3145,38 +3145,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478359</v>
+        <v>478406</v>
       </c>
       <c r="R24" t="n">
-        <v>6950978</v>
+        <v>6950869</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178252</v>
+        <v>122178465</v>
       </c>
       <c r="B25" t="n">
-        <v>97139</v>
+        <v>98206</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3251,34 +3251,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478406</v>
+        <v>478530</v>
       </c>
       <c r="R25" t="n">
-        <v>6950869</v>
+        <v>6951133</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,10 +3337,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178362</v>
+        <v>122178253</v>
       </c>
       <c r="B26" t="n">
-        <v>98102</v>
+        <v>78646</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478333</v>
+        <v>478328</v>
       </c>
       <c r="R26" t="n">
-        <v>6950917</v>
+        <v>6950727</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178446</v>
+        <v>122178453</v>
       </c>
       <c r="B27" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,34 +3455,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478494</v>
+        <v>478446</v>
       </c>
       <c r="R27" t="n">
-        <v>6950958</v>
+        <v>6951134</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178457</v>
+        <v>122178450</v>
       </c>
       <c r="B28" t="n">
-        <v>79727</v>
+        <v>97139</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3553,25 +3553,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478413</v>
+        <v>478475</v>
       </c>
       <c r="R28" t="n">
-        <v>6951171</v>
+        <v>6951076</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178463</v>
+        <v>122178363</v>
       </c>
       <c r="B29" t="n">
-        <v>98206</v>
+        <v>78646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3655,38 +3655,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478493</v>
+        <v>478331</v>
       </c>
       <c r="R29" t="n">
-        <v>6951137</v>
+        <v>6950917</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3713,12 +3713,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,7 +3745,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178447</v>
+        <v>122178452</v>
       </c>
       <c r="B30" t="n">
         <v>78646</v>
@@ -3781,14 +3781,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478465</v>
+        <v>478438</v>
       </c>
       <c r="R30" t="n">
-        <v>6950995</v>
+        <v>6951070</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3847,10 +3847,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178461</v>
+        <v>122178448</v>
       </c>
       <c r="B31" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3863,21 +3863,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478474</v>
+        <v>478499</v>
       </c>
       <c r="R31" t="n">
-        <v>6951157</v>
+        <v>6951053</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178451</v>
+        <v>122178444</v>
       </c>
       <c r="B32" t="n">
-        <v>74739</v>
+        <v>97139</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3961,38 +3961,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478444</v>
+        <v>478443</v>
       </c>
       <c r="R32" t="n">
-        <v>6951071</v>
+        <v>6950943</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,7 +4051,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178455</v>
+        <v>122178361</v>
       </c>
       <c r="B33" t="n">
         <v>97139</v>
@@ -4087,14 +4087,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478417</v>
+        <v>478441</v>
       </c>
       <c r="R33" t="n">
-        <v>6951155</v>
+        <v>6950927</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178450</v>
+        <v>122178442</v>
       </c>
       <c r="B34" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4193,10 +4193,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478475</v>
+        <v>478328</v>
       </c>
       <c r="R34" t="n">
-        <v>6951076</v>
+        <v>6951010</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4223,12 +4223,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4255,7 +4255,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178464</v>
+        <v>122178459</v>
       </c>
       <c r="B35" t="n">
         <v>97139</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478526</v>
+        <v>478424</v>
       </c>
       <c r="R35" t="n">
-        <v>6951125</v>
+        <v>6951178</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178363</v>
+        <v>122178463</v>
       </c>
       <c r="B36" t="n">
-        <v>78646</v>
+        <v>98206</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4369,38 +4369,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478331</v>
+        <v>478493</v>
       </c>
       <c r="R36" t="n">
-        <v>6950917</v>
+        <v>6951137</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4427,12 +4427,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4459,10 +4459,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178454</v>
+        <v>122178449</v>
       </c>
       <c r="B37" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478433</v>
+        <v>478483</v>
       </c>
       <c r="R37" t="n">
-        <v>6951141</v>
+        <v>6951051</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178452</v>
+        <v>122178454</v>
       </c>
       <c r="B38" t="n">
         <v>78646</v>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478438</v>
+        <v>478433</v>
       </c>
       <c r="R38" t="n">
-        <v>6951070</v>
+        <v>6951141</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178448</v>
+        <v>122178362</v>
       </c>
       <c r="B39" t="n">
-        <v>78646</v>
+        <v>98102</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4675,38 +4675,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478499</v>
+        <v>478333</v>
       </c>
       <c r="R39" t="n">
-        <v>6951053</v>
+        <v>6950917</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4733,12 +4733,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4765,10 +4765,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178456</v>
+        <v>122178457</v>
       </c>
       <c r="B40" t="n">
-        <v>79763</v>
+        <v>79727</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4777,25 +4777,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478417</v>
+        <v>478413</v>
       </c>
       <c r="R40" t="n">
-        <v>6951176</v>
+        <v>6951171</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178459</v>
+        <v>122178456</v>
       </c>
       <c r="B41" t="n">
-        <v>97139</v>
+        <v>79763</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4883,21 +4883,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478424</v>
+        <v>478417</v>
       </c>
       <c r="R41" t="n">
-        <v>6951178</v>
+        <v>6951176</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178361</v>
+        <v>122178446</v>
       </c>
       <c r="B42" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478441</v>
+        <v>478494</v>
       </c>
       <c r="R42" t="n">
-        <v>6950927</v>
+        <v>6950958</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5071,7 +5071,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178449</v>
+        <v>122178461</v>
       </c>
       <c r="B43" t="n">
         <v>79727</v>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478483</v>
+        <v>478474</v>
       </c>
       <c r="R43" t="n">
-        <v>6951051</v>
+        <v>6951157</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178253</v>
+        <v>122178460</v>
       </c>
       <c r="B44" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5185,38 +5185,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478328</v>
+        <v>478446</v>
       </c>
       <c r="R44" t="n">
-        <v>6950727</v>
+        <v>6951151</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178453</v>
+        <v>122178455</v>
       </c>
       <c r="B45" t="n">
-        <v>79727</v>
+        <v>97139</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478446</v>
+        <v>478417</v>
       </c>
       <c r="R45" t="n">
-        <v>6951134</v>
+        <v>6951155</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2725,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178464</v>
+        <v>122178447</v>
       </c>
       <c r="B20" t="n">
-        <v>97139</v>
+        <v>78646</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,38 +2737,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478526</v>
+        <v>478465</v>
       </c>
       <c r="R20" t="n">
-        <v>6951125</v>
+        <v>6950995</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178447</v>
+        <v>122178443</v>
       </c>
       <c r="B21" t="n">
         <v>78646</v>
@@ -2863,14 +2863,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478465</v>
+        <v>478359</v>
       </c>
       <c r="R21" t="n">
-        <v>6950995</v>
+        <v>6950978</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178443</v>
+        <v>122178464</v>
       </c>
       <c r="B22" t="n">
-        <v>78646</v>
+        <v>97139</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478359</v>
+        <v>478526</v>
       </c>
       <c r="R22" t="n">
-        <v>6950978</v>
+        <v>6951125</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2614,7 +2614,7 @@
         <v>122154997</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178447</v>
+        <v>122178460</v>
       </c>
       <c r="B20" t="n">
-        <v>78646</v>
+        <v>97151</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,38 +2737,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478465</v>
+        <v>478446</v>
       </c>
       <c r="R20" t="n">
-        <v>6950995</v>
+        <v>6951151</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178443</v>
+        <v>122178451</v>
       </c>
       <c r="B21" t="n">
-        <v>78646</v>
+        <v>74744</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478359</v>
+        <v>478444</v>
       </c>
       <c r="R21" t="n">
-        <v>6950978</v>
+        <v>6951071</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178464</v>
+        <v>122178443</v>
       </c>
       <c r="B22" t="n">
-        <v>97139</v>
+        <v>78651</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478526</v>
+        <v>478359</v>
       </c>
       <c r="R22" t="n">
-        <v>6951125</v>
+        <v>6950978</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3031,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178451</v>
+        <v>122178465</v>
       </c>
       <c r="B23" t="n">
-        <v>74739</v>
+        <v>98218</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,25 +3043,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478444</v>
+        <v>478530</v>
       </c>
       <c r="R23" t="n">
-        <v>6951071</v>
+        <v>6951133</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178252</v>
+        <v>122178453</v>
       </c>
       <c r="B24" t="n">
-        <v>97139</v>
+        <v>79732</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3145,38 +3145,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478406</v>
+        <v>478446</v>
       </c>
       <c r="R24" t="n">
-        <v>6950869</v>
+        <v>6951134</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178465</v>
+        <v>122178363</v>
       </c>
       <c r="B25" t="n">
-        <v>98206</v>
+        <v>78651</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3247,38 +3247,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478530</v>
+        <v>478331</v>
       </c>
       <c r="R25" t="n">
-        <v>6951133</v>
+        <v>6950917</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,10 +3337,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178253</v>
+        <v>122178448</v>
       </c>
       <c r="B26" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3373,14 +3373,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478328</v>
+        <v>478499</v>
       </c>
       <c r="R26" t="n">
-        <v>6950727</v>
+        <v>6951053</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178453</v>
+        <v>122178252</v>
       </c>
       <c r="B27" t="n">
-        <v>79727</v>
+        <v>97151</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3451,38 +3451,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478446</v>
+        <v>478406</v>
       </c>
       <c r="R27" t="n">
-        <v>6951134</v>
+        <v>6950869</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,10 +3541,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178450</v>
+        <v>122178444</v>
       </c>
       <c r="B28" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3577,14 +3577,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478475</v>
+        <v>478443</v>
       </c>
       <c r="R28" t="n">
-        <v>6951076</v>
+        <v>6950943</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178363</v>
+        <v>122178454</v>
       </c>
       <c r="B29" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3679,14 +3679,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478331</v>
+        <v>478433</v>
       </c>
       <c r="R29" t="n">
-        <v>6950917</v>
+        <v>6951141</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3713,12 +3713,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178452</v>
+        <v>122178253</v>
       </c>
       <c r="B30" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3781,14 +3781,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478438</v>
+        <v>478328</v>
       </c>
       <c r="R30" t="n">
-        <v>6951070</v>
+        <v>6950727</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178448</v>
+        <v>122178450</v>
       </c>
       <c r="B31" t="n">
-        <v>78646</v>
+        <v>97151</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3859,25 +3859,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478499</v>
+        <v>478475</v>
       </c>
       <c r="R31" t="n">
-        <v>6951053</v>
+        <v>6951076</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178444</v>
+        <v>122178447</v>
       </c>
       <c r="B32" t="n">
-        <v>97139</v>
+        <v>78651</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3961,25 +3961,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478443</v>
+        <v>478465</v>
       </c>
       <c r="R32" t="n">
-        <v>6950943</v>
+        <v>6950995</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178361</v>
+        <v>122178464</v>
       </c>
       <c r="B33" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4087,14 +4087,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478441</v>
+        <v>478526</v>
       </c>
       <c r="R33" t="n">
-        <v>6950927</v>
+        <v>6951125</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,10 +4153,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178442</v>
+        <v>122178361</v>
       </c>
       <c r="B34" t="n">
-        <v>78646</v>
+        <v>97151</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4165,38 +4165,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478328</v>
+        <v>478441</v>
       </c>
       <c r="R34" t="n">
-        <v>6951010</v>
+        <v>6950927</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178459</v>
+        <v>122178455</v>
       </c>
       <c r="B35" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478424</v>
+        <v>478417</v>
       </c>
       <c r="R35" t="n">
-        <v>6951178</v>
+        <v>6951155</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178463</v>
+        <v>122178446</v>
       </c>
       <c r="B36" t="n">
-        <v>98206</v>
+        <v>78651</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4369,38 +4369,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478493</v>
+        <v>478494</v>
       </c>
       <c r="R36" t="n">
-        <v>6951137</v>
+        <v>6950958</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178449</v>
+        <v>122178463</v>
       </c>
       <c r="B37" t="n">
-        <v>79727</v>
+        <v>98218</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4471,25 +4471,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478483</v>
+        <v>478493</v>
       </c>
       <c r="R37" t="n">
-        <v>6951051</v>
+        <v>6951137</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178454</v>
+        <v>122178449</v>
       </c>
       <c r="B38" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478433</v>
+        <v>478483</v>
       </c>
       <c r="R38" t="n">
-        <v>6951141</v>
+        <v>6951051</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178362</v>
+        <v>122178459</v>
       </c>
       <c r="B39" t="n">
-        <v>98102</v>
+        <v>97151</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4679,34 +4679,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478333</v>
+        <v>478424</v>
       </c>
       <c r="R39" t="n">
-        <v>6950917</v>
+        <v>6951178</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4733,12 +4733,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4768,7 +4768,7 @@
         <v>122178457</v>
       </c>
       <c r="B40" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178456</v>
+        <v>122178461</v>
       </c>
       <c r="B41" t="n">
-        <v>79763</v>
+        <v>79732</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,25 +4879,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4907,10 +4907,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478417</v>
+        <v>478474</v>
       </c>
       <c r="R41" t="n">
-        <v>6951176</v>
+        <v>6951157</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178446</v>
+        <v>122178452</v>
       </c>
       <c r="B42" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5005,14 +5005,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478494</v>
+        <v>478438</v>
       </c>
       <c r="R42" t="n">
-        <v>6950958</v>
+        <v>6951070</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178461</v>
+        <v>122178442</v>
       </c>
       <c r="B43" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5087,21 +5087,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478474</v>
+        <v>478328</v>
       </c>
       <c r="R43" t="n">
-        <v>6951157</v>
+        <v>6951010</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5173,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178460</v>
+        <v>122178456</v>
       </c>
       <c r="B44" t="n">
-        <v>97139</v>
+        <v>79768</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478446</v>
+        <v>478417</v>
       </c>
       <c r="R44" t="n">
-        <v>6951151</v>
+        <v>6951176</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178455</v>
+        <v>122178362</v>
       </c>
       <c r="B45" t="n">
-        <v>97139</v>
+        <v>98114</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5291,34 +5291,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478417</v>
+        <v>478333</v>
       </c>
       <c r="R45" t="n">
-        <v>6951155</v>
+        <v>6950917</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5345,12 +5345,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2725,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178460</v>
+        <v>122178443</v>
       </c>
       <c r="B20" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,25 +2737,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478446</v>
+        <v>478359</v>
       </c>
       <c r="R20" t="n">
-        <v>6951151</v>
+        <v>6950978</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,10 +2827,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178451</v>
+        <v>122178460</v>
       </c>
       <c r="B21" t="n">
-        <v>74744</v>
+        <v>97156</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,25 +2839,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478444</v>
+        <v>478446</v>
       </c>
       <c r="R21" t="n">
-        <v>6951071</v>
+        <v>6951151</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178443</v>
+        <v>122178463</v>
       </c>
       <c r="B22" t="n">
-        <v>78651</v>
+        <v>98223</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,25 +2941,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478359</v>
+        <v>478493</v>
       </c>
       <c r="R22" t="n">
-        <v>6950978</v>
+        <v>6951137</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,7 +3034,7 @@
         <v>122178465</v>
       </c>
       <c r="B23" t="n">
-        <v>98218</v>
+        <v>98223</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178453</v>
+        <v>122178363</v>
       </c>
       <c r="B24" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3149,34 +3149,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478446</v>
+        <v>478331</v>
       </c>
       <c r="R24" t="n">
-        <v>6951134</v>
+        <v>6950917</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,7 +3235,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178363</v>
+        <v>122178253</v>
       </c>
       <c r="B25" t="n">
         <v>78651</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478331</v>
+        <v>478328</v>
       </c>
       <c r="R25" t="n">
-        <v>6950917</v>
+        <v>6950727</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,10 +3337,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178448</v>
+        <v>122178459</v>
       </c>
       <c r="B26" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3349,25 +3349,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478499</v>
+        <v>478424</v>
       </c>
       <c r="R26" t="n">
-        <v>6951053</v>
+        <v>6951178</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178252</v>
+        <v>122178452</v>
       </c>
       <c r="B27" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3451,38 +3451,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478406</v>
+        <v>478438</v>
       </c>
       <c r="R27" t="n">
-        <v>6950869</v>
+        <v>6951070</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,10 +3541,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178444</v>
+        <v>122178449</v>
       </c>
       <c r="B28" t="n">
-        <v>97151</v>
+        <v>79732</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3553,38 +3553,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478443</v>
+        <v>478483</v>
       </c>
       <c r="R28" t="n">
-        <v>6950943</v>
+        <v>6951051</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178454</v>
+        <v>122178450</v>
       </c>
       <c r="B29" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478433</v>
+        <v>478475</v>
       </c>
       <c r="R29" t="n">
-        <v>6951141</v>
+        <v>6951076</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178253</v>
+        <v>122178455</v>
       </c>
       <c r="B30" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3757,38 +3757,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478328</v>
+        <v>478417</v>
       </c>
       <c r="R30" t="n">
-        <v>6950727</v>
+        <v>6951155</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3847,10 +3847,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178450</v>
+        <v>122178457</v>
       </c>
       <c r="B31" t="n">
-        <v>97151</v>
+        <v>79732</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3859,25 +3859,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478475</v>
+        <v>478413</v>
       </c>
       <c r="R31" t="n">
-        <v>6951076</v>
+        <v>6951171</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178447</v>
+        <v>122178453</v>
       </c>
       <c r="B32" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3965,34 +3965,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478465</v>
+        <v>478446</v>
       </c>
       <c r="R32" t="n">
-        <v>6950995</v>
+        <v>6951134</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178464</v>
+        <v>122178451</v>
       </c>
       <c r="B33" t="n">
-        <v>97151</v>
+        <v>74744</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4063,25 +4063,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478526</v>
+        <v>478444</v>
       </c>
       <c r="R33" t="n">
-        <v>6951125</v>
+        <v>6951071</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4156,7 +4156,7 @@
         <v>122178361</v>
       </c>
       <c r="B34" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178455</v>
+        <v>122178454</v>
       </c>
       <c r="B35" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4267,25 +4267,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478417</v>
+        <v>478433</v>
       </c>
       <c r="R35" t="n">
-        <v>6951155</v>
+        <v>6951141</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4459,10 +4459,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178463</v>
+        <v>122178464</v>
       </c>
       <c r="B37" t="n">
-        <v>98218</v>
+        <v>97156</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478493</v>
+        <v>478526</v>
       </c>
       <c r="R37" t="n">
-        <v>6951137</v>
+        <v>6951125</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178449</v>
+        <v>122178252</v>
       </c>
       <c r="B38" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4573,38 +4573,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478483</v>
+        <v>478406</v>
       </c>
       <c r="R38" t="n">
-        <v>6951051</v>
+        <v>6950869</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4631,12 +4631,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4663,10 +4663,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178459</v>
+        <v>122178447</v>
       </c>
       <c r="B39" t="n">
-        <v>97151</v>
+        <v>78651</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4675,38 +4675,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478424</v>
+        <v>478465</v>
       </c>
       <c r="R39" t="n">
-        <v>6951178</v>
+        <v>6950995</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4765,10 +4765,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178457</v>
+        <v>122178456</v>
       </c>
       <c r="B40" t="n">
-        <v>79732</v>
+        <v>79768</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4777,25 +4777,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478413</v>
+        <v>478417</v>
       </c>
       <c r="R40" t="n">
-        <v>6951171</v>
+        <v>6951176</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178461</v>
+        <v>122178444</v>
       </c>
       <c r="B41" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,38 +4879,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478474</v>
+        <v>478443</v>
       </c>
       <c r="R41" t="n">
-        <v>6951157</v>
+        <v>6950943</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4969,7 +4969,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178452</v>
+        <v>122178442</v>
       </c>
       <c r="B42" t="n">
         <v>78651</v>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478438</v>
+        <v>478328</v>
       </c>
       <c r="R42" t="n">
-        <v>6951070</v>
+        <v>6951010</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5071,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178442</v>
+        <v>122178461</v>
       </c>
       <c r="B43" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5087,21 +5087,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478328</v>
+        <v>478474</v>
       </c>
       <c r="R43" t="n">
-        <v>6951010</v>
+        <v>6951157</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5173,10 +5173,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178456</v>
+        <v>122178448</v>
       </c>
       <c r="B44" t="n">
-        <v>79768</v>
+        <v>78651</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5185,25 +5185,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478417</v>
+        <v>478499</v>
       </c>
       <c r="R44" t="n">
-        <v>6951176</v>
+        <v>6951053</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5278,7 +5278,7 @@
         <v>122178362</v>
       </c>
       <c r="B45" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2611,14 +2611,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122154997</v>
+        <v>122178443</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2627,46 +2627,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478569</v>
+        <v>478359</v>
       </c>
       <c r="R19" t="n">
-        <v>6950967</v>
+        <v>6950978</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2693,12 +2681,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,22 +2701,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Veronica Lindström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178443</v>
+        <v>122178460</v>
       </c>
       <c r="B20" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,25 +2725,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2765,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478359</v>
+        <v>478446</v>
       </c>
       <c r="R20" t="n">
-        <v>6950978</v>
+        <v>6951151</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2795,12 +2783,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178460</v>
+        <v>122178463</v>
       </c>
       <c r="B21" t="n">
-        <v>97156</v>
+        <v>98223</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2843,21 +2831,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478446</v>
+        <v>478493</v>
       </c>
       <c r="R21" t="n">
-        <v>6951151</v>
+        <v>6951137</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2929,7 +2917,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178463</v>
+        <v>122178465</v>
       </c>
       <c r="B22" t="n">
         <v>98223</v>
@@ -2969,10 +2957,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478493</v>
+        <v>478530</v>
       </c>
       <c r="R22" t="n">
-        <v>6951137</v>
+        <v>6951133</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3031,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178465</v>
+        <v>122178363</v>
       </c>
       <c r="B23" t="n">
-        <v>98223</v>
+        <v>78651</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,38 +3031,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478530</v>
+        <v>478331</v>
       </c>
       <c r="R23" t="n">
-        <v>6951133</v>
+        <v>6950917</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3101,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3133,7 +3121,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178363</v>
+        <v>122178253</v>
       </c>
       <c r="B24" t="n">
         <v>78651</v>
@@ -3173,10 +3161,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478331</v>
+        <v>478328</v>
       </c>
       <c r="R24" t="n">
-        <v>6950917</v>
+        <v>6950727</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3203,12 +3191,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3223,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178253</v>
+        <v>122178459</v>
       </c>
       <c r="B25" t="n">
-        <v>78651</v>
+        <v>97156</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3247,38 +3235,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478328</v>
+        <v>478424</v>
       </c>
       <c r="R25" t="n">
-        <v>6950727</v>
+        <v>6951178</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3305,12 +3293,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3337,10 +3325,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178459</v>
+        <v>122178452</v>
       </c>
       <c r="B26" t="n">
-        <v>97156</v>
+        <v>78651</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3349,25 +3337,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3377,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478424</v>
+        <v>478438</v>
       </c>
       <c r="R26" t="n">
-        <v>6951178</v>
+        <v>6951070</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3439,10 +3427,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178452</v>
+        <v>122178449</v>
       </c>
       <c r="B27" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,21 +3443,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3479,10 +3467,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478438</v>
+        <v>478483</v>
       </c>
       <c r="R27" t="n">
-        <v>6951070</v>
+        <v>6951051</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3541,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178449</v>
+        <v>122178450</v>
       </c>
       <c r="B28" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3553,25 +3541,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3581,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478483</v>
+        <v>478475</v>
       </c>
       <c r="R28" t="n">
-        <v>6951051</v>
+        <v>6951076</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3643,7 +3631,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178450</v>
+        <v>122178455</v>
       </c>
       <c r="B29" t="n">
         <v>97156</v>
@@ -3683,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478475</v>
+        <v>478417</v>
       </c>
       <c r="R29" t="n">
-        <v>6951076</v>
+        <v>6951155</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3745,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178455</v>
+        <v>122178457</v>
       </c>
       <c r="B30" t="n">
-        <v>97156</v>
+        <v>79732</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3757,25 +3745,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3785,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478417</v>
+        <v>478413</v>
       </c>
       <c r="R30" t="n">
-        <v>6951155</v>
+        <v>6951171</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3847,7 +3835,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178457</v>
+        <v>122178453</v>
       </c>
       <c r="B31" t="n">
         <v>79732</v>
@@ -3887,10 +3875,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478413</v>
+        <v>478446</v>
       </c>
       <c r="R31" t="n">
-        <v>6951171</v>
+        <v>6951134</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3949,10 +3937,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178453</v>
+        <v>122178451</v>
       </c>
       <c r="B32" t="n">
-        <v>79732</v>
+        <v>74744</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3965,21 +3953,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3989,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478446</v>
+        <v>478444</v>
       </c>
       <c r="R32" t="n">
-        <v>6951134</v>
+        <v>6951071</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4051,10 +4039,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178451</v>
+        <v>122178361</v>
       </c>
       <c r="B33" t="n">
-        <v>74744</v>
+        <v>97156</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4063,38 +4051,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478444</v>
+        <v>478441</v>
       </c>
       <c r="R33" t="n">
-        <v>6951071</v>
+        <v>6950927</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4121,12 +4109,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4153,10 +4141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178361</v>
+        <v>122178454</v>
       </c>
       <c r="B34" t="n">
-        <v>97156</v>
+        <v>78651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4165,38 +4153,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478441</v>
+        <v>478433</v>
       </c>
       <c r="R34" t="n">
-        <v>6950927</v>
+        <v>6951141</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4223,12 +4211,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4255,7 +4243,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178454</v>
+        <v>122178446</v>
       </c>
       <c r="B35" t="n">
         <v>78651</v>
@@ -4291,14 +4279,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478433</v>
+        <v>478494</v>
       </c>
       <c r="R35" t="n">
-        <v>6951141</v>
+        <v>6950958</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4357,7 +4345,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178446</v>
+        <v>122178447</v>
       </c>
       <c r="B36" t="n">
         <v>78651</v>
@@ -4397,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478494</v>
+        <v>478465</v>
       </c>
       <c r="R36" t="n">
-        <v>6950958</v>
+        <v>6950995</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4663,10 +4651,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178447</v>
+        <v>122178456</v>
       </c>
       <c r="B39" t="n">
-        <v>78651</v>
+        <v>79768</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4675,38 +4663,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478465</v>
+        <v>478417</v>
       </c>
       <c r="R39" t="n">
-        <v>6950995</v>
+        <v>6951176</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4765,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178456</v>
+        <v>122178444</v>
       </c>
       <c r="B40" t="n">
-        <v>79768</v>
+        <v>97156</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4781,34 +4769,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478417</v>
+        <v>478443</v>
       </c>
       <c r="R40" t="n">
-        <v>6951176</v>
+        <v>6950943</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4835,12 +4823,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178444</v>
+        <v>122178442</v>
       </c>
       <c r="B41" t="n">
-        <v>97156</v>
+        <v>78651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4879,38 +4867,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478443</v>
+        <v>478328</v>
       </c>
       <c r="R41" t="n">
-        <v>6950943</v>
+        <v>6951010</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4969,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178442</v>
+        <v>122178461</v>
       </c>
       <c r="B42" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4985,21 +4973,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478328</v>
+        <v>478474</v>
       </c>
       <c r="R42" t="n">
-        <v>6951010</v>
+        <v>6951157</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5039,12 +5027,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5071,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178461</v>
+        <v>122178448</v>
       </c>
       <c r="B43" t="n">
-        <v>79732</v>
+        <v>78651</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5087,21 +5075,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5111,10 +5099,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478474</v>
+        <v>478499</v>
       </c>
       <c r="R43" t="n">
-        <v>6951157</v>
+        <v>6951053</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5173,10 +5161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178448</v>
+        <v>122178362</v>
       </c>
       <c r="B44" t="n">
-        <v>78651</v>
+        <v>98119</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5185,38 +5173,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478499</v>
+        <v>478333</v>
       </c>
       <c r="R44" t="n">
-        <v>6951053</v>
+        <v>6950917</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5243,12 +5231,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5275,50 +5263,62 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122178362</v>
+        <v>122154997</v>
       </c>
       <c r="B45" t="n">
-        <v>98119</v>
+        <v>57379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478333</v>
+        <v>478569</v>
       </c>
       <c r="R45" t="n">
-        <v>6950917</v>
+        <v>6950967</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5345,12 +5345,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5365,12 +5365,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Veronica Lindström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178443</v>
+        <v>122178456</v>
       </c>
       <c r="B19" t="n">
-        <v>78651</v>
+        <v>79769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,25 +2623,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6464</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2651,10 +2646,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478359</v>
+        <v>478417</v>
       </c>
       <c r="R19" t="n">
-        <v>6950978</v>
+        <v>6951176</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2681,12 +2676,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2713,10 +2708,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178460</v>
+        <v>122178361</v>
       </c>
       <c r="B20" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,11 +2726,6 @@
       <c r="E20" t="n">
         <v>221945</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -2749,14 +2739,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478446</v>
+        <v>478441</v>
       </c>
       <c r="R20" t="n">
-        <v>6951151</v>
+        <v>6950927</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2783,12 +2773,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178463</v>
+        <v>122178253</v>
       </c>
       <c r="B21" t="n">
-        <v>98223</v>
+        <v>78652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2827,38 +2817,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478493</v>
+        <v>478328</v>
       </c>
       <c r="R21" t="n">
-        <v>6951137</v>
+        <v>6950727</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2885,12 +2870,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178465</v>
+        <v>122178444</v>
       </c>
       <c r="B22" t="n">
-        <v>98223</v>
+        <v>97165</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,34 +2918,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478530</v>
+        <v>478443</v>
       </c>
       <c r="R22" t="n">
-        <v>6951133</v>
+        <v>6950943</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2987,12 +2967,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,10 +2999,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178363</v>
+        <v>122178463</v>
       </c>
       <c r="B23" t="n">
-        <v>78651</v>
+        <v>98232</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3031,38 +3011,33 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478331</v>
+        <v>478493</v>
       </c>
       <c r="R23" t="n">
-        <v>6950917</v>
+        <v>6951137</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3089,12 +3064,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3121,10 +3096,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178253</v>
+        <v>122178455</v>
       </c>
       <c r="B24" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3133,38 +3108,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478328</v>
+        <v>478417</v>
       </c>
       <c r="R24" t="n">
-        <v>6950727</v>
+        <v>6951155</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3191,12 +3161,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,10 +3193,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178459</v>
+        <v>122178465</v>
       </c>
       <c r="B25" t="n">
-        <v>97156</v>
+        <v>98232</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3239,21 +3209,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>221952</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3263,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478424</v>
+        <v>478530</v>
       </c>
       <c r="R25" t="n">
-        <v>6951178</v>
+        <v>6951133</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3325,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178452</v>
+        <v>122178459</v>
       </c>
       <c r="B26" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3337,25 +3302,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478438</v>
+        <v>478424</v>
       </c>
       <c r="R26" t="n">
-        <v>6951070</v>
+        <v>6951178</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3427,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178449</v>
+        <v>122178446</v>
       </c>
       <c r="B27" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3443,34 +3403,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478483</v>
+        <v>478494</v>
       </c>
       <c r="R27" t="n">
-        <v>6951051</v>
+        <v>6950958</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3532,7 +3487,7 @@
         <v>122178450</v>
       </c>
       <c r="B28" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3546,11 +3501,6 @@
       </c>
       <c r="E28" t="n">
         <v>221945</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3631,10 +3581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178455</v>
+        <v>122178448</v>
       </c>
       <c r="B29" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3643,25 +3593,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,10 +3616,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478417</v>
+        <v>478499</v>
       </c>
       <c r="R29" t="n">
-        <v>6951155</v>
+        <v>6951053</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3733,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178457</v>
+        <v>122178451</v>
       </c>
       <c r="B30" t="n">
-        <v>79732</v>
+        <v>74745</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3749,21 +3694,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>308</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478413</v>
+        <v>478444</v>
       </c>
       <c r="R30" t="n">
-        <v>6951171</v>
+        <v>6951071</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3835,10 +3775,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178453</v>
+        <v>122178447</v>
       </c>
       <c r="B31" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3851,34 +3791,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478446</v>
+        <v>478465</v>
       </c>
       <c r="R31" t="n">
-        <v>6951134</v>
+        <v>6950995</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3937,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178451</v>
+        <v>122178457</v>
       </c>
       <c r="B32" t="n">
-        <v>74744</v>
+        <v>79733</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3953,21 +3888,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3977,10 +3907,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478444</v>
+        <v>478413</v>
       </c>
       <c r="R32" t="n">
-        <v>6951071</v>
+        <v>6951171</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4039,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178361</v>
+        <v>122178443</v>
       </c>
       <c r="B33" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4051,38 +3981,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478441</v>
+        <v>478359</v>
       </c>
       <c r="R33" t="n">
-        <v>6950927</v>
+        <v>6950978</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4141,10 +4066,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178454</v>
+        <v>122178461</v>
       </c>
       <c r="B34" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4157,21 +4082,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4181,10 +4101,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478433</v>
+        <v>478474</v>
       </c>
       <c r="R34" t="n">
-        <v>6951141</v>
+        <v>6951157</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4243,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178446</v>
+        <v>122178453</v>
       </c>
       <c r="B35" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4259,34 +4179,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478494</v>
+        <v>478446</v>
       </c>
       <c r="R35" t="n">
-        <v>6950958</v>
+        <v>6951134</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4345,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178447</v>
+        <v>122178464</v>
       </c>
       <c r="B36" t="n">
-        <v>78651</v>
+        <v>97165</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4357,38 +4272,33 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478465</v>
+        <v>478526</v>
       </c>
       <c r="R36" t="n">
-        <v>6950995</v>
+        <v>6951125</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4447,10 +4357,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178464</v>
+        <v>122178362</v>
       </c>
       <c r="B37" t="n">
-        <v>97156</v>
+        <v>98128</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4463,34 +4373,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>219790</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478526</v>
+        <v>478333</v>
       </c>
       <c r="R37" t="n">
-        <v>6951125</v>
+        <v>6950917</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4517,12 +4422,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,10 +4454,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178252</v>
+        <v>122178452</v>
       </c>
       <c r="B38" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4561,38 +4466,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478406</v>
+        <v>478438</v>
       </c>
       <c r="R38" t="n">
-        <v>6950869</v>
+        <v>6951070</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4619,12 +4519,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4651,10 +4551,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178456</v>
+        <v>122178363</v>
       </c>
       <c r="B39" t="n">
-        <v>79768</v>
+        <v>78652</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4663,38 +4563,33 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478417</v>
+        <v>478331</v>
       </c>
       <c r="R39" t="n">
-        <v>6951176</v>
+        <v>6950917</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4721,12 +4616,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4753,10 +4648,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178444</v>
+        <v>122178454</v>
       </c>
       <c r="B40" t="n">
-        <v>97156</v>
+        <v>78652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4765,38 +4660,33 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478443</v>
+        <v>478433</v>
       </c>
       <c r="R40" t="n">
-        <v>6950943</v>
+        <v>6951141</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4823,12 +4713,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4858,7 +4748,7 @@
         <v>122178442</v>
       </c>
       <c r="B41" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4872,11 +4762,6 @@
       </c>
       <c r="E41" t="n">
         <v>6425</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4957,10 +4842,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178461</v>
+        <v>122178252</v>
       </c>
       <c r="B42" t="n">
-        <v>79732</v>
+        <v>97165</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4969,38 +4854,33 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478474</v>
+        <v>478406</v>
       </c>
       <c r="R42" t="n">
-        <v>6951157</v>
+        <v>6950869</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5027,12 +4907,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,10 +4939,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178448</v>
+        <v>122178449</v>
       </c>
       <c r="B43" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5075,21 +4955,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5099,10 +4974,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478499</v>
+        <v>478483</v>
       </c>
       <c r="R43" t="n">
-        <v>6951053</v>
+        <v>6951051</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5161,10 +5036,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178362</v>
+        <v>122178460</v>
       </c>
       <c r="B44" t="n">
-        <v>98119</v>
+        <v>97165</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5177,34 +5052,29 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478333</v>
+        <v>478446</v>
       </c>
       <c r="R44" t="n">
-        <v>6950917</v>
+        <v>6951151</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5231,12 +5101,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5280,11 +5150,6 @@
       </c>
       <c r="E45" t="n">
         <v>100109</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2805,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178253</v>
+        <v>122178444</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>97165</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2817,20 +2817,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478328</v>
+        <v>478443</v>
       </c>
       <c r="R21" t="n">
-        <v>6950727</v>
+        <v>6950943</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178444</v>
+        <v>122178253</v>
       </c>
       <c r="B22" t="n">
-        <v>97165</v>
+        <v>78652</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478443</v>
+        <v>478328</v>
       </c>
       <c r="R22" t="n">
-        <v>6950943</v>
+        <v>6950727</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3581,10 +3581,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178448</v>
+        <v>122178451</v>
       </c>
       <c r="B29" t="n">
-        <v>78652</v>
+        <v>74745</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478499</v>
+        <v>478444</v>
       </c>
       <c r="R29" t="n">
-        <v>6951053</v>
+        <v>6951071</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178451</v>
+        <v>122178448</v>
       </c>
       <c r="B30" t="n">
-        <v>74745</v>
+        <v>78652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478444</v>
+        <v>478499</v>
       </c>
       <c r="R30" t="n">
-        <v>6951071</v>
+        <v>6951053</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178443</v>
+        <v>122178461</v>
       </c>
       <c r="B33" t="n">
-        <v>78652</v>
+        <v>79733</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3985,16 +3985,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478359</v>
+        <v>478474</v>
       </c>
       <c r="R33" t="n">
-        <v>6950978</v>
+        <v>6951157</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,10 +4066,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178461</v>
+        <v>122178443</v>
       </c>
       <c r="B34" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4082,16 +4082,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478474</v>
+        <v>478359</v>
       </c>
       <c r="R34" t="n">
-        <v>6951157</v>
+        <v>6950978</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2805,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178444</v>
+        <v>122178253</v>
       </c>
       <c r="B21" t="n">
-        <v>97165</v>
+        <v>78652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2817,20 +2817,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478443</v>
+        <v>478328</v>
       </c>
       <c r="R21" t="n">
-        <v>6950943</v>
+        <v>6950727</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178253</v>
+        <v>122178444</v>
       </c>
       <c r="B22" t="n">
-        <v>78652</v>
+        <v>97165</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,20 +2914,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478328</v>
+        <v>478443</v>
       </c>
       <c r="R22" t="n">
-        <v>6950727</v>
+        <v>6950943</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178459</v>
+        <v>122178446</v>
       </c>
       <c r="B26" t="n">
-        <v>97165</v>
+        <v>78652</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,33 +3302,33 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478424</v>
+        <v>478494</v>
       </c>
       <c r="R26" t="n">
-        <v>6951178</v>
+        <v>6950958</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178446</v>
+        <v>122178459</v>
       </c>
       <c r="B27" t="n">
-        <v>78652</v>
+        <v>97165</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3399,33 +3399,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478494</v>
+        <v>478424</v>
       </c>
       <c r="R27" t="n">
-        <v>6950958</v>
+        <v>6951178</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178447</v>
+        <v>122178457</v>
       </c>
       <c r="B31" t="n">
-        <v>78652</v>
+        <v>79733</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,29 +3791,29 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478465</v>
+        <v>478413</v>
       </c>
       <c r="R31" t="n">
-        <v>6950995</v>
+        <v>6951171</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178457</v>
+        <v>122178447</v>
       </c>
       <c r="B32" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3888,29 +3888,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478413</v>
+        <v>478465</v>
       </c>
       <c r="R32" t="n">
-        <v>6951171</v>
+        <v>6950995</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178461</v>
+        <v>122178443</v>
       </c>
       <c r="B33" t="n">
-        <v>79733</v>
+        <v>78652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3985,16 +3985,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478474</v>
+        <v>478359</v>
       </c>
       <c r="R33" t="n">
-        <v>6951157</v>
+        <v>6950978</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,10 +4066,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178443</v>
+        <v>122178461</v>
       </c>
       <c r="B34" t="n">
-        <v>78652</v>
+        <v>79733</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4082,16 +4082,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478359</v>
+        <v>478474</v>
       </c>
       <c r="R34" t="n">
-        <v>6950978</v>
+        <v>6951157</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178456</v>
+        <v>122178459</v>
       </c>
       <c r="B19" t="n">
-        <v>79769</v>
+        <v>97178</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,16 +2627,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2646,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478417</v>
+        <v>478424</v>
       </c>
       <c r="R19" t="n">
-        <v>6951176</v>
+        <v>6951178</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2708,10 +2713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178361</v>
+        <v>122178448</v>
       </c>
       <c r="B20" t="n">
-        <v>97165</v>
+        <v>78656</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,33 +2725,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478441</v>
+        <v>478499</v>
       </c>
       <c r="R20" t="n">
-        <v>6950927</v>
+        <v>6951053</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2773,12 +2783,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178253</v>
+        <v>122178456</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>79773</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2817,33 +2827,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478328</v>
+        <v>478417</v>
       </c>
       <c r="R21" t="n">
-        <v>6950727</v>
+        <v>6951176</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2870,12 +2885,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2902,10 +2917,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178444</v>
+        <v>122178465</v>
       </c>
       <c r="B22" t="n">
-        <v>97165</v>
+        <v>98245</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2918,29 +2933,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>221952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478443</v>
+        <v>478530</v>
       </c>
       <c r="R22" t="n">
-        <v>6950943</v>
+        <v>6951133</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2967,12 +2987,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178463</v>
+        <v>122178253</v>
       </c>
       <c r="B23" t="n">
-        <v>98232</v>
+        <v>78656</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3011,33 +3031,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478493</v>
+        <v>478328</v>
       </c>
       <c r="R23" t="n">
-        <v>6951137</v>
+        <v>6950727</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178455</v>
+        <v>122178362</v>
       </c>
       <c r="B24" t="n">
-        <v>97165</v>
+        <v>98141</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3112,29 +3137,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>219790</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478417</v>
+        <v>478333</v>
       </c>
       <c r="R24" t="n">
-        <v>6951155</v>
+        <v>6950917</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3161,12 +3191,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,10 +3223,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178465</v>
+        <v>122178461</v>
       </c>
       <c r="B25" t="n">
-        <v>98232</v>
+        <v>79737</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3205,20 +3235,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3263,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478530</v>
+        <v>478474</v>
       </c>
       <c r="R25" t="n">
-        <v>6951133</v>
+        <v>6951157</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3290,10 +3325,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178446</v>
+        <v>122178457</v>
       </c>
       <c r="B26" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,29 +3341,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478494</v>
+        <v>478413</v>
       </c>
       <c r="R26" t="n">
-        <v>6950958</v>
+        <v>6951171</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3387,10 +3427,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178459</v>
+        <v>122178464</v>
       </c>
       <c r="B27" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3405,6 +3445,11 @@
       <c r="E27" t="n">
         <v>221945</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -3422,10 +3467,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478424</v>
+        <v>478526</v>
       </c>
       <c r="R27" t="n">
-        <v>6951178</v>
+        <v>6951125</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3484,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178450</v>
+        <v>122178460</v>
       </c>
       <c r="B28" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,6 +3547,11 @@
       <c r="E28" t="n">
         <v>221945</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -3519,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478475</v>
+        <v>478446</v>
       </c>
       <c r="R28" t="n">
-        <v>6951076</v>
+        <v>6951151</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3581,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178451</v>
+        <v>122178363</v>
       </c>
       <c r="B29" t="n">
-        <v>74745</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3597,29 +3647,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478444</v>
+        <v>478331</v>
       </c>
       <c r="R29" t="n">
-        <v>6951071</v>
+        <v>6950917</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3646,12 +3701,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3678,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178448</v>
+        <v>122178444</v>
       </c>
       <c r="B30" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3690,33 +3745,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478499</v>
+        <v>478443</v>
       </c>
       <c r="R30" t="n">
-        <v>6951053</v>
+        <v>6950943</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3743,12 +3803,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,10 +3835,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178457</v>
+        <v>122178451</v>
       </c>
       <c r="B31" t="n">
-        <v>79733</v>
+        <v>74749</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3791,16 +3851,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>308</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3810,10 +3875,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478413</v>
+        <v>478444</v>
       </c>
       <c r="R31" t="n">
-        <v>6951171</v>
+        <v>6951071</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3872,10 +3937,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178447</v>
+        <v>122178252</v>
       </c>
       <c r="B32" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3884,20 +3949,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3907,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478465</v>
+        <v>478406</v>
       </c>
       <c r="R32" t="n">
-        <v>6950995</v>
+        <v>6950869</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3937,12 +4007,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3969,10 +4039,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178443</v>
+        <v>122178447</v>
       </c>
       <c r="B33" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3987,6 +4057,11 @@
       <c r="E33" t="n">
         <v>6425</v>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4000,14 +4075,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478359</v>
+        <v>478465</v>
       </c>
       <c r="R33" t="n">
-        <v>6950978</v>
+        <v>6950995</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4034,12 +4109,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,10 +4141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178461</v>
+        <v>122178443</v>
       </c>
       <c r="B34" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4082,16 +4157,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4101,10 +4181,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478474</v>
+        <v>478359</v>
       </c>
       <c r="R34" t="n">
-        <v>6951157</v>
+        <v>6950978</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4131,12 +4211,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4163,10 +4243,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178453</v>
+        <v>122178452</v>
       </c>
       <c r="B35" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4179,16 +4259,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4198,10 +4283,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478446</v>
+        <v>478438</v>
       </c>
       <c r="R35" t="n">
-        <v>6951134</v>
+        <v>6951070</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4260,10 +4345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178464</v>
+        <v>122178449</v>
       </c>
       <c r="B36" t="n">
-        <v>97165</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,20 +4357,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478526</v>
+        <v>478483</v>
       </c>
       <c r="R36" t="n">
-        <v>6951125</v>
+        <v>6951051</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4357,10 +4447,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178362</v>
+        <v>122178454</v>
       </c>
       <c r="B37" t="n">
-        <v>98128</v>
+        <v>78656</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,33 +4459,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219790</v>
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478333</v>
+        <v>478433</v>
       </c>
       <c r="R37" t="n">
-        <v>6950917</v>
+        <v>6951141</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4422,12 +4517,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4454,10 +4549,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178452</v>
+        <v>122178442</v>
       </c>
       <c r="B38" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4472,6 +4567,11 @@
       <c r="E38" t="n">
         <v>6425</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -4489,10 +4589,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478438</v>
+        <v>478328</v>
       </c>
       <c r="R38" t="n">
-        <v>6951070</v>
+        <v>6951010</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4519,12 +4619,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4551,10 +4651,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178363</v>
+        <v>122178450</v>
       </c>
       <c r="B39" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4563,33 +4663,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478331</v>
+        <v>478475</v>
       </c>
       <c r="R39" t="n">
-        <v>6950917</v>
+        <v>6951076</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4616,12 +4721,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4648,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178454</v>
+        <v>122178463</v>
       </c>
       <c r="B40" t="n">
-        <v>78652</v>
+        <v>98245</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4660,20 +4765,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>221952</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4683,10 +4793,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478433</v>
+        <v>478493</v>
       </c>
       <c r="R40" t="n">
-        <v>6951141</v>
+        <v>6951137</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4745,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178442</v>
+        <v>122178455</v>
       </c>
       <c r="B41" t="n">
-        <v>78652</v>
+        <v>97178</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4757,20 +4867,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4780,10 +4895,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478328</v>
+        <v>478417</v>
       </c>
       <c r="R41" t="n">
-        <v>6951010</v>
+        <v>6951155</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4810,12 +4925,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4842,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178252</v>
+        <v>122178361</v>
       </c>
       <c r="B42" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4860,6 +4975,11 @@
       <c r="E42" t="n">
         <v>221945</v>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Lycopodium annotinum</t>
@@ -4877,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478406</v>
+        <v>478441</v>
       </c>
       <c r="R42" t="n">
-        <v>6950869</v>
+        <v>6950927</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4907,12 +5027,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4939,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178449</v>
+        <v>122178446</v>
       </c>
       <c r="B43" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4955,29 +5075,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478483</v>
+        <v>478494</v>
       </c>
       <c r="R43" t="n">
-        <v>6951051</v>
+        <v>6950958</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5036,10 +5161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178460</v>
+        <v>122178453</v>
       </c>
       <c r="B44" t="n">
-        <v>97165</v>
+        <v>79737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5048,20 +5173,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5074,7 +5204,7 @@
         <v>478446</v>
       </c>
       <c r="R44" t="n">
-        <v>6951151</v>
+        <v>6951134</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5136,7 +5266,7 @@
         <v>122154997</v>
       </c>
       <c r="B45" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5150,6 +5280,11 @@
       </c>
       <c r="E45" t="n">
         <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178459</v>
+        <v>122178455</v>
       </c>
       <c r="B19" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478424</v>
+        <v>478417</v>
       </c>
       <c r="R19" t="n">
-        <v>6951178</v>
+        <v>6951155</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2713,10 +2713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178448</v>
+        <v>122178457</v>
       </c>
       <c r="B20" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478499</v>
+        <v>478413</v>
       </c>
       <c r="R20" t="n">
-        <v>6951053</v>
+        <v>6951171</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178456</v>
+        <v>122178449</v>
       </c>
       <c r="B21" t="n">
-        <v>79773</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2827,25 +2827,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478417</v>
+        <v>478483</v>
       </c>
       <c r="R21" t="n">
-        <v>6951176</v>
+        <v>6951051</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178465</v>
+        <v>122178363</v>
       </c>
       <c r="B22" t="n">
-        <v>98245</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2929,38 +2929,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478530</v>
+        <v>478331</v>
       </c>
       <c r="R22" t="n">
-        <v>6951133</v>
+        <v>6950917</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2987,12 +2987,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178253</v>
+        <v>122178465</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>98258</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3031,38 +3031,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478328</v>
+        <v>478530</v>
       </c>
       <c r="R23" t="n">
-        <v>6950727</v>
+        <v>6951133</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178362</v>
+        <v>122178446</v>
       </c>
       <c r="B24" t="n">
-        <v>98141</v>
+        <v>78656</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3133,25 +3133,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478333</v>
+        <v>478494</v>
       </c>
       <c r="R24" t="n">
-        <v>6950917</v>
+        <v>6950958</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,10 +3223,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178461</v>
+        <v>122178362</v>
       </c>
       <c r="B25" t="n">
-        <v>79737</v>
+        <v>98154</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3235,38 +3235,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478474</v>
+        <v>478333</v>
       </c>
       <c r="R25" t="n">
-        <v>6951157</v>
+        <v>6950917</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,12 +3293,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178457</v>
+        <v>122178459</v>
       </c>
       <c r="B26" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3337,25 +3337,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478413</v>
+        <v>478424</v>
       </c>
       <c r="R26" t="n">
-        <v>6951171</v>
+        <v>6951178</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178464</v>
+        <v>122178447</v>
       </c>
       <c r="B27" t="n">
-        <v>97178</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3439,38 +3439,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478526</v>
+        <v>478465</v>
       </c>
       <c r="R27" t="n">
-        <v>6951125</v>
+        <v>6950995</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178460</v>
+        <v>122178361</v>
       </c>
       <c r="B28" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3565,14 +3565,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478446</v>
+        <v>478441</v>
       </c>
       <c r="R28" t="n">
-        <v>6951151</v>
+        <v>6950927</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178363</v>
+        <v>122178252</v>
       </c>
       <c r="B29" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3643,25 +3643,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478331</v>
+        <v>478406</v>
       </c>
       <c r="R29" t="n">
-        <v>6950917</v>
+        <v>6950869</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178444</v>
+        <v>122178453</v>
       </c>
       <c r="B30" t="n">
-        <v>97178</v>
+        <v>79737</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3745,38 +3745,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478443</v>
+        <v>478446</v>
       </c>
       <c r="R30" t="n">
-        <v>6950943</v>
+        <v>6951134</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,10 +3835,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122178451</v>
+        <v>122178253</v>
       </c>
       <c r="B31" t="n">
-        <v>74749</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3851,34 +3851,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478444</v>
+        <v>478328</v>
       </c>
       <c r="R31" t="n">
-        <v>6951071</v>
+        <v>6950727</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3937,10 +3937,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178252</v>
+        <v>122178460</v>
       </c>
       <c r="B32" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3973,14 +3973,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478406</v>
+        <v>478446</v>
       </c>
       <c r="R32" t="n">
-        <v>6950869</v>
+        <v>6951151</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4007,12 +4007,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,7 +4039,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178447</v>
+        <v>122178443</v>
       </c>
       <c r="B33" t="n">
         <v>78656</v>
@@ -4075,14 +4075,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478465</v>
+        <v>478359</v>
       </c>
       <c r="R33" t="n">
-        <v>6950995</v>
+        <v>6950978</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,10 +4141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178443</v>
+        <v>122178464</v>
       </c>
       <c r="B34" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4153,25 +4153,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478359</v>
+        <v>478526</v>
       </c>
       <c r="R34" t="n">
-        <v>6950978</v>
+        <v>6951125</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4243,7 +4243,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178452</v>
+        <v>122178454</v>
       </c>
       <c r="B35" t="n">
         <v>78656</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478438</v>
+        <v>478433</v>
       </c>
       <c r="R35" t="n">
-        <v>6951070</v>
+        <v>6951141</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178449</v>
+        <v>122178452</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4361,21 +4361,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478483</v>
+        <v>478438</v>
       </c>
       <c r="R36" t="n">
-        <v>6951051</v>
+        <v>6951070</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178454</v>
+        <v>122178442</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478433</v>
+        <v>478328</v>
       </c>
       <c r="R37" t="n">
-        <v>6951141</v>
+        <v>6951010</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4517,12 +4517,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,10 +4549,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178442</v>
+        <v>122178461</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4565,21 +4565,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478328</v>
+        <v>478474</v>
       </c>
       <c r="R38" t="n">
-        <v>6951010</v>
+        <v>6951157</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178450</v>
+        <v>122178448</v>
       </c>
       <c r="B39" t="n">
-        <v>97178</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4663,25 +4663,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478475</v>
+        <v>478499</v>
       </c>
       <c r="R39" t="n">
-        <v>6951076</v>
+        <v>6951053</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178463</v>
+        <v>122178450</v>
       </c>
       <c r="B40" t="n">
-        <v>98245</v>
+        <v>97191</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478493</v>
+        <v>478475</v>
       </c>
       <c r="R40" t="n">
-        <v>6951137</v>
+        <v>6951076</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178455</v>
+        <v>122178451</v>
       </c>
       <c r="B41" t="n">
-        <v>97178</v>
+        <v>74749</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478417</v>
+        <v>478444</v>
       </c>
       <c r="R41" t="n">
-        <v>6951155</v>
+        <v>6951071</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4957,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178361</v>
+        <v>122178463</v>
       </c>
       <c r="B42" t="n">
-        <v>97178</v>
+        <v>98258</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4973,34 +4973,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478441</v>
+        <v>478493</v>
       </c>
       <c r="R42" t="n">
-        <v>6950927</v>
+        <v>6951137</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5027,12 +5027,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178446</v>
+        <v>122178456</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
+        <v>79773</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5071,38 +5071,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478494</v>
+        <v>478417</v>
       </c>
       <c r="R43" t="n">
-        <v>6950958</v>
+        <v>6951176</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5161,10 +5161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178453</v>
+        <v>122178444</v>
       </c>
       <c r="B44" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5173,38 +5173,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478446</v>
+        <v>478443</v>
       </c>
       <c r="R44" t="n">
-        <v>6951134</v>
+        <v>6950943</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -2611,10 +2611,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122178455</v>
+        <v>122178463</v>
       </c>
       <c r="B19" t="n">
-        <v>97191</v>
+        <v>98258</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478417</v>
+        <v>478493</v>
       </c>
       <c r="R19" t="n">
-        <v>6951155</v>
+        <v>6951137</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2713,10 +2713,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122178457</v>
+        <v>122178451</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>74749</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478413</v>
+        <v>478444</v>
       </c>
       <c r="R20" t="n">
-        <v>6951171</v>
+        <v>6951071</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122178449</v>
+        <v>122178460</v>
       </c>
       <c r="B21" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2827,25 +2827,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478483</v>
+        <v>478446</v>
       </c>
       <c r="R21" t="n">
-        <v>6951051</v>
+        <v>6951151</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2917,7 +2917,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122178363</v>
+        <v>122178442</v>
       </c>
       <c r="B22" t="n">
         <v>78656</v>
@@ -2953,14 +2953,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478331</v>
+        <v>478328</v>
       </c>
       <c r="R22" t="n">
-        <v>6950917</v>
+        <v>6951010</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122178465</v>
+        <v>122178444</v>
       </c>
       <c r="B23" t="n">
-        <v>98258</v>
+        <v>97191</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3035,34 +3035,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478530</v>
+        <v>478443</v>
       </c>
       <c r="R23" t="n">
-        <v>6951133</v>
+        <v>6950943</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3089,12 +3089,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3121,10 +3121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122178446</v>
+        <v>122178450</v>
       </c>
       <c r="B24" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3133,38 +3133,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478494</v>
+        <v>478475</v>
       </c>
       <c r="R24" t="n">
-        <v>6950958</v>
+        <v>6951076</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122178362</v>
+        <v>122178447</v>
       </c>
       <c r="B25" t="n">
-        <v>98154</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3235,25 +3235,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478333</v>
+        <v>478465</v>
       </c>
       <c r="R25" t="n">
-        <v>6950917</v>
+        <v>6950995</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3293,12 +3293,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122178459</v>
+        <v>122178461</v>
       </c>
       <c r="B26" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3337,25 +3337,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478424</v>
+        <v>478474</v>
       </c>
       <c r="R26" t="n">
-        <v>6951178</v>
+        <v>6951157</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122178447</v>
+        <v>122178363</v>
       </c>
       <c r="B27" t="n">
         <v>78656</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478465</v>
+        <v>478331</v>
       </c>
       <c r="R27" t="n">
-        <v>6950995</v>
+        <v>6950917</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3497,12 +3497,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122178361</v>
+        <v>122178446</v>
       </c>
       <c r="B28" t="n">
-        <v>97191</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3541,25 +3541,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478441</v>
+        <v>478494</v>
       </c>
       <c r="R28" t="n">
-        <v>6950927</v>
+        <v>6950958</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122178252</v>
+        <v>122178448</v>
       </c>
       <c r="B29" t="n">
-        <v>97191</v>
+        <v>78656</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3643,38 +3643,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478406</v>
+        <v>478499</v>
       </c>
       <c r="R29" t="n">
-        <v>6950869</v>
+        <v>6951053</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3733,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122178453</v>
+        <v>122178464</v>
       </c>
       <c r="B30" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3745,25 +3745,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478446</v>
+        <v>478526</v>
       </c>
       <c r="R30" t="n">
-        <v>6951134</v>
+        <v>6951125</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3937,10 +3937,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122178460</v>
+        <v>122178449</v>
       </c>
       <c r="B32" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3949,25 +3949,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478446</v>
+        <v>478483</v>
       </c>
       <c r="R32" t="n">
-        <v>6951151</v>
+        <v>6951051</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4039,10 +4039,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122178443</v>
+        <v>122178459</v>
       </c>
       <c r="B33" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4051,25 +4051,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478359</v>
+        <v>478424</v>
       </c>
       <c r="R33" t="n">
-        <v>6950978</v>
+        <v>6951178</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,10 +4141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122178464</v>
+        <v>122178362</v>
       </c>
       <c r="B34" t="n">
-        <v>97191</v>
+        <v>98154</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4157,34 +4157,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478526</v>
+        <v>478333</v>
       </c>
       <c r="R34" t="n">
-        <v>6951125</v>
+        <v>6950917</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4243,10 +4243,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122178454</v>
+        <v>122178455</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478433</v>
+        <v>478417</v>
       </c>
       <c r="R35" t="n">
-        <v>6951141</v>
+        <v>6951155</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4345,10 +4345,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122178452</v>
+        <v>122178361</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>97191</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4357,38 +4357,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478438</v>
+        <v>478441</v>
       </c>
       <c r="R36" t="n">
-        <v>6951070</v>
+        <v>6950927</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4447,7 +4447,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122178442</v>
+        <v>122178443</v>
       </c>
       <c r="B37" t="n">
         <v>78656</v>
@@ -4487,10 +4487,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478328</v>
+        <v>478359</v>
       </c>
       <c r="R37" t="n">
-        <v>6951010</v>
+        <v>6950978</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122178461</v>
+        <v>122178252</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
+        <v>97191</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4561,38 +4561,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergsvik-Gammalbodarna, Jmt</t>
+          <t>Bergsvik, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478474</v>
+        <v>478406</v>
       </c>
       <c r="R38" t="n">
-        <v>6951157</v>
+        <v>6950869</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4619,12 +4619,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122178448</v>
+        <v>122178456</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>79773</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4663,25 +4663,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478499</v>
+        <v>478417</v>
       </c>
       <c r="R39" t="n">
-        <v>6951053</v>
+        <v>6951176</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122178450</v>
+        <v>122178457</v>
       </c>
       <c r="B40" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4765,25 +4765,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478475</v>
+        <v>478413</v>
       </c>
       <c r="R40" t="n">
-        <v>6951076</v>
+        <v>6951171</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122178451</v>
+        <v>122178452</v>
       </c>
       <c r="B41" t="n">
-        <v>74749</v>
+        <v>78656</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478444</v>
+        <v>478438</v>
       </c>
       <c r="R41" t="n">
-        <v>6951071</v>
+        <v>6951070</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4957,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122178463</v>
+        <v>122178454</v>
       </c>
       <c r="B42" t="n">
-        <v>98258</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4969,25 +4969,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478493</v>
+        <v>478433</v>
       </c>
       <c r="R42" t="n">
-        <v>6951137</v>
+        <v>6951141</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5059,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122178456</v>
+        <v>122178465</v>
       </c>
       <c r="B43" t="n">
-        <v>79773</v>
+        <v>98258</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5075,21 +5075,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478417</v>
+        <v>478530</v>
       </c>
       <c r="R43" t="n">
-        <v>6951176</v>
+        <v>6951133</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5161,10 +5161,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122178444</v>
+        <v>122178453</v>
       </c>
       <c r="B44" t="n">
-        <v>97191</v>
+        <v>79737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5173,38 +5173,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergsvik, Jmt</t>
+          <t>Bergsvik-Gammalbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478443</v>
+        <v>478446</v>
       </c>
       <c r="R44" t="n">
-        <v>6950943</v>
+        <v>6951134</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5375,6 +5375,350 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125657672</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56836</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>478264</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6950675</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125657695</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57627</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>478319</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6950643</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125657696</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>478458</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6950871</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Par som trummar och varnar</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -6726,10 +6726,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>75066</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6737,37 +6737,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R59" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6794,9 +6794,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6811,22 +6821,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B60" t="n">
-        <v>75066</v>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6834,37 +6844,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R60" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6891,19 +6901,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6918,12 +6918,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5377,44 +5377,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125657696</v>
+        <v>125657672</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5424,10 +5423,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478458</v>
+        <v>478264</v>
       </c>
       <c r="R46" t="n">
-        <v>6950871</v>
+        <v>6950675</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5454,17 +5453,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Par som trummar och varnar</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5484,17 +5478,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125657695</v>
+        <v>125733533</v>
       </c>
       <c r="B47" t="n">
-        <v>57643</v>
+        <v>80099</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5502,44 +5496,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100110</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478319</v>
+        <v>478241</v>
       </c>
       <c r="R47" t="n">
-        <v>6950643</v>
+        <v>6950681</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5566,12 +5550,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5586,68 +5570,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125657672</v>
+        <v>125733382</v>
       </c>
       <c r="B48" t="n">
-        <v>56843</v>
+        <v>80070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478264</v>
+        <v>478271</v>
       </c>
       <c r="R48" t="n">
-        <v>6950675</v>
+        <v>6950713</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,12 +5647,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5694,44 +5667,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125733533</v>
+        <v>125733394</v>
       </c>
       <c r="B49" t="n">
-        <v>80099</v>
+        <v>80071</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5741,10 +5714,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478241</v>
+        <v>478271</v>
       </c>
       <c r="R49" t="n">
-        <v>6950681</v>
+        <v>6950713</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5803,7 +5776,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125733382</v>
+        <v>125733513</v>
       </c>
       <c r="B50" t="n">
         <v>80070</v>
@@ -5838,10 +5811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478271</v>
+        <v>478241</v>
       </c>
       <c r="R50" t="n">
-        <v>6950713</v>
+        <v>6950681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5900,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125733394</v>
+        <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>80071</v>
+        <v>78967</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5911,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478271</v>
+        <v>478493</v>
       </c>
       <c r="R51" t="n">
-        <v>6950713</v>
+        <v>6950911</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5965,12 +5938,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5985,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125733513</v>
+        <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6008,37 +5991,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478241</v>
+        <v>478282</v>
       </c>
       <c r="R52" t="n">
-        <v>6950681</v>
+        <v>6950863</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6062,12 +6045,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6082,19 +6080,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125791362</v>
+        <v>125791318</v>
       </c>
       <c r="B53" t="n">
         <v>57651</v>
@@ -6123,19 +6121,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478282</v>
+        <v>478301</v>
       </c>
       <c r="R53" t="n">
-        <v>6950863</v>
+        <v>6950878</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6162,24 +6165,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Pågående bobygge</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6194,22 +6187,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125802798</v>
+        <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>91245</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6217,37 +6210,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478493</v>
+        <v>478287</v>
       </c>
       <c r="R54" t="n">
-        <v>6950911</v>
+        <v>6950870</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6274,19 +6267,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>09:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6301,22 +6284,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125791318</v>
+        <v>125794889</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6324,39 +6307,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478301</v>
+        <v>478257</v>
       </c>
       <c r="R55" t="n">
-        <v>6950878</v>
+        <v>6950700</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6389,11 +6367,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6420,10 +6393,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125791295</v>
+        <v>125802837</v>
       </c>
       <c r="B56" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6431,37 +6404,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478287</v>
+        <v>478266</v>
       </c>
       <c r="R56" t="n">
-        <v>6950870</v>
+        <v>6950684</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6488,9 +6461,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>relativt färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6505,22 +6493,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125794889</v>
+        <v>125802810</v>
       </c>
       <c r="B57" t="n">
-        <v>80071</v>
+        <v>75066</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6528,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478257</v>
+        <v>478284</v>
       </c>
       <c r="R57" t="n">
-        <v>6950700</v>
+        <v>6950882</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6585,9 +6573,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6602,22 +6600,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125802837</v>
+        <v>125790953</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6625,37 +6623,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478266</v>
+        <v>478485</v>
       </c>
       <c r="R58" t="n">
-        <v>6950684</v>
+        <v>6950915</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6682,24 +6680,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>relativt färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6714,22 +6697,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125802810</v>
+        <v>125794895</v>
       </c>
       <c r="B59" t="n">
-        <v>75066</v>
+        <v>80070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6737,37 +6720,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478284</v>
+        <v>478250</v>
       </c>
       <c r="R59" t="n">
-        <v>6950882</v>
+        <v>6950721</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6794,19 +6777,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6821,60 +6794,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125790953</v>
+        <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478485</v>
+        <v>478363</v>
       </c>
       <c r="R60" t="n">
-        <v>6950915</v>
+        <v>6950902</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6901,9 +6874,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6918,22 +6901,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125794895</v>
+        <v>125833010</v>
       </c>
       <c r="B61" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6941,37 +6924,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478250</v>
+        <v>478554</v>
       </c>
       <c r="R61" t="n">
-        <v>6950721</v>
+        <v>6950972</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7001,6 +6984,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7015,60 +7003,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125802809</v>
+        <v>125833012</v>
       </c>
       <c r="B62" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478363</v>
+        <v>478601</v>
       </c>
       <c r="R62" t="n">
-        <v>6950902</v>
+        <v>6950938</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7095,19 +7083,14 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>09:30</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7122,19 +7105,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125833010</v>
+        <v>125833016</v>
       </c>
       <c r="B63" t="n">
         <v>57651</v>
@@ -7169,10 +7152,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478554</v>
+        <v>478266</v>
       </c>
       <c r="R63" t="n">
-        <v>6950972</v>
+        <v>6950686</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7209,7 +7192,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7236,7 +7219,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125833012</v>
+        <v>125833011</v>
       </c>
       <c r="B64" t="n">
         <v>57651</v>
@@ -7271,10 +7254,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478601</v>
+        <v>478571</v>
       </c>
       <c r="R64" t="n">
-        <v>6950938</v>
+        <v>6950954</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7338,7 +7321,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125833016</v>
+        <v>125657696</v>
       </c>
       <c r="B65" t="n">
         <v>57651</v>
@@ -7366,17 +7349,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478266</v>
+        <v>478458</v>
       </c>
       <c r="R65" t="n">
-        <v>6950686</v>
+        <v>6950871</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7403,17 +7398,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Par som trummar och varnar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7428,57 +7423,67 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125833011</v>
+        <v>125657695</v>
       </c>
       <c r="B66" t="n">
-        <v>57651</v>
+        <v>57643</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kläppberget, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478571</v>
+        <v>478319</v>
       </c>
       <c r="R66" t="n">
-        <v>6950954</v>
+        <v>6950643</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7505,17 +7510,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7530,12 +7530,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5876,7 +5876,7 @@
         <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>125794889</v>
       </c>
       <c r="B55" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B57" t="n">
-        <v>75066</v>
+        <v>78968</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R57" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,19 +6573,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,22 +6590,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>75067</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6623,37 +6613,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R58" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,9 +6670,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6712,7 +6712,7 @@
         <v>125794895</v>
       </c>
       <c r="B59" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5488,7 +5488,7 @@
         <v>125733533</v>
       </c>
       <c r="B47" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>125733382</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>125733394</v>
       </c>
       <c r="B49" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>125733513</v>
       </c>
       <c r="B50" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R51" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,7 +5953,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,22 +5973,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B52" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5991,37 +5996,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R52" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6060,12 +6065,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R51" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,12 +5953,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5996,37 +5991,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R52" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6065,7 +6060,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B57" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R57" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,9 +6573,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6590,22 +6600,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B58" t="n">
-        <v>75067</v>
+        <v>78968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6613,37 +6623,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R58" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6670,19 +6680,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5488,7 +5488,7 @@
         <v>125733533</v>
       </c>
       <c r="B47" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>125733382</v>
       </c>
       <c r="B48" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>125733394</v>
       </c>
       <c r="B49" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>125733513</v>
       </c>
       <c r="B50" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>125794889</v>
       </c>
       <c r="B55" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B57" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R57" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,19 +6573,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,22 +6590,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B58" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6623,37 +6613,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R58" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,9 +6670,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6712,7 +6712,7 @@
         <v>125794895</v>
       </c>
       <c r="B59" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R51" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,7 +5953,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,22 +5973,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B52" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5991,37 +5996,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R52" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6060,12 +6065,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>75067</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R57" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,9 +6573,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6590,22 +6600,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B58" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6613,37 +6623,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R58" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6670,19 +6680,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R51" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,12 +5953,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5996,37 +5991,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R52" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6065,7 +6060,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B57" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R57" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,19 +6573,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,22 +6590,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>75067</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6623,37 +6613,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R58" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,9 +6670,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R51" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,7 +5953,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,22 +5973,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B52" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5991,37 +5996,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R52" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6060,12 +6065,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5380,7 +5380,7 @@
         <v>125657672</v>
       </c>
       <c r="B46" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>125733533</v>
       </c>
       <c r="B47" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>125733382</v>
       </c>
       <c r="B48" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>125733394</v>
       </c>
       <c r="B49" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>125733513</v>
       </c>
       <c r="B50" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>125791362</v>
       </c>
       <c r="B51" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>125802798</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>125791318</v>
       </c>
       <c r="B53" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>125794889</v>
       </c>
       <c r="B55" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>125802837</v>
       </c>
       <c r="B56" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>75068</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R57" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,9 +6573,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6590,22 +6600,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B58" t="n">
-        <v>75067</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6613,37 +6623,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R58" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6670,19 +6680,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6712,7 +6712,7 @@
         <v>125794895</v>
       </c>
       <c r="B59" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>125833010</v>
       </c>
       <c r="B61" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>125833012</v>
       </c>
       <c r="B62" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>125833016</v>
       </c>
       <c r="B63" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>125833011</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>125657696</v>
       </c>
       <c r="B65" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>125657695</v>
       </c>
       <c r="B66" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R51" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,12 +5953,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5996,37 +5991,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R52" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6065,7 +6060,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R51" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,7 +5953,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,22 +5973,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B52" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5991,37 +5996,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R52" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6060,12 +6065,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
         <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B57" t="n">
-        <v>75068</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R57" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,19 +6573,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,22 +6590,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>75068</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6623,37 +6613,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R58" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,9 +6670,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>75068</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R57" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,9 +6573,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6590,22 +6600,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B58" t="n">
-        <v>75068</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6613,37 +6623,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R58" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6670,19 +6680,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R51" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,12 +5953,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5996,37 +5991,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R52" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6065,7 +6060,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6202,7 +6202,7 @@
         <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B57" t="n">
-        <v>75068</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R57" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,19 +6573,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,22 +6590,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>75068</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6623,37 +6613,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R58" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,9 +6670,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R51" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,7 +5953,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,22 +5973,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B52" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5991,37 +5996,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R52" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6060,12 +6065,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5380,7 +5380,7 @@
         <v>125657672</v>
       </c>
       <c r="B46" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>125733533</v>
       </c>
       <c r="B47" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>125733382</v>
       </c>
       <c r="B48" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>125733394</v>
       </c>
       <c r="B49" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>125733513</v>
       </c>
       <c r="B50" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R51" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,12 +5953,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5996,37 +5991,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R52" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6065,7 +6060,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
         <v>125791318</v>
       </c>
       <c r="B53" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>125794889</v>
       </c>
       <c r="B55" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>125802837</v>
       </c>
       <c r="B56" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>125790953</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>125802810</v>
       </c>
       <c r="B58" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>125794895</v>
       </c>
       <c r="B59" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>125833010</v>
       </c>
       <c r="B61" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>125833012</v>
       </c>
       <c r="B62" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>125833016</v>
       </c>
       <c r="B63" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>125833011</v>
       </c>
       <c r="B64" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>125657696</v>
       </c>
       <c r="B65" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>125657695</v>
       </c>
       <c r="B66" t="n">
-        <v>57644</v>
+        <v>57648</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R57" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,9 +6573,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6590,22 +6600,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B58" t="n">
-        <v>75072</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6613,37 +6623,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R58" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6670,19 +6680,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R51" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,7 +5953,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,22 +5973,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5991,37 +5996,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R52" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6050,7 +6055,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6060,12 +6065,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B57" t="n">
-        <v>75072</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R57" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,19 +6573,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6600,22 +6590,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6623,37 +6613,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R58" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,9 +6670,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5873,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125791362</v>
+        <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5884,37 +5884,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478282</v>
+        <v>478493</v>
       </c>
       <c r="R51" t="n">
-        <v>6950863</v>
+        <v>6950911</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5953,12 +5953,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Pågående bobygge</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125802798</v>
+        <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5996,37 +5991,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478493</v>
+        <v>478282</v>
       </c>
       <c r="R52" t="n">
-        <v>6950911</v>
+        <v>6950863</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6055,7 +6050,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6065,7 +6060,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Pågående bobygge</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6080,12 +6080,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -5876,7 +5876,7 @@
         <v>125802798</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>125791362</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>125791318</v>
       </c>
       <c r="B53" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>125791295</v>
       </c>
       <c r="B54" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>125794889</v>
       </c>
       <c r="B55" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>125802837</v>
       </c>
       <c r="B56" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125790953</v>
+        <v>125802810</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>75075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6516,37 +6516,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kläppvallen, Kläppvallen, Jmt</t>
+          <t>kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478485</v>
+        <v>478284</v>
       </c>
       <c r="R57" t="n">
-        <v>6950915</v>
+        <v>6950882</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,9 +6573,19 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6590,22 +6600,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125802810</v>
+        <v>125790953</v>
       </c>
       <c r="B58" t="n">
-        <v>75072</v>
+        <v>78980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6613,37 +6623,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>kläppberget, Jmt</t>
+          <t>Kläppvallen, Kläppvallen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478284</v>
+        <v>478485</v>
       </c>
       <c r="R58" t="n">
-        <v>6950882</v>
+        <v>6950915</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6670,19 +6680,9 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6697,12 +6697,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6712,7 +6712,7 @@
         <v>125794895</v>
       </c>
       <c r="B59" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>125802809</v>
       </c>
       <c r="B60" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         <v>125833010</v>
       </c>
       <c r="B61" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>125833012</v>
       </c>
       <c r="B62" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>125833016</v>
       </c>
       <c r="B63" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>125833011</v>
       </c>
       <c r="B64" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>125657696</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>125657695</v>
       </c>
       <c r="B66" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7540,6 +7540,336 @@
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127340288</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98463</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>478369</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6950796</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Galileo Empower AB - Brynje</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127340285</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98463</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>478478</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6950741</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Galileo Empower AB - Brynje</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>127340287</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98359</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>478372</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6950798</v>
+      </c>
+      <c r="S69" t="n">
+        <v>4</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Galileo Empower AB - Brynje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 17952-2024 artfynd.xlsx
+++ b/artfynd/A 17952-2024 artfynd.xlsx
@@ -7545,7 +7545,7 @@
         <v>127340288</v>
       </c>
       <c r="B67" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>127340285</v>
       </c>
       <c r="B68" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>127340287</v>
       </c>
       <c r="B69" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
